--- a/assets/excel/customer_manager_info.xlsx
+++ b/assets/excel/customer_manager_info.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>客户经理编号</t>
   </si>
@@ -37,18 +37,21 @@
   <si>
     <t>客户经理手机号码</t>
   </si>
+  <si>
+    <t>团队编码</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -61,6 +64,13 @@
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -541,156 +551,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1226,13 +1239,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="3" width="16.7211538461538" customWidth="1"/>
+    <col min="4" max="4" width="18.2692307692308" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1242,6 +1256,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
